--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,70 +471,553 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46203</v>
+        <v>44620</v>
       </c>
       <c r="B2" t="n">
-        <v>147426</v>
+        <v>112335</v>
       </c>
       <c r="C2" t="n">
-        <v>45537</v>
+        <v>60961</v>
       </c>
       <c r="D2" t="n">
-        <v>94250</v>
+        <v>43535</v>
       </c>
       <c r="E2" t="n">
-        <v>-17667</v>
+        <v>-57729</v>
       </c>
       <c r="F2" t="n">
-        <v>1806</v>
+        <v>-3153</v>
       </c>
       <c r="G2" t="n">
-        <v>-15861</v>
+        <v>-60882</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46206</v>
+        <v>44624</v>
       </c>
       <c r="B3" t="n">
-        <v>159694</v>
+        <v>110261</v>
       </c>
       <c r="C3" t="n">
-        <v>54276</v>
+        <v>60319</v>
       </c>
       <c r="D3" t="n">
-        <v>97742</v>
+        <v>42081</v>
       </c>
       <c r="E3" t="n">
-        <v>-17580</v>
+        <v>-57267</v>
       </c>
       <c r="F3" t="n">
-        <v>2535</v>
+        <v>-3528</v>
       </c>
       <c r="G3" t="n">
-        <v>-15045</v>
+        <v>-60795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
+        <v>44631</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108864</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57497</v>
+      </c>
+      <c r="D4" t="n">
+        <v>43528</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-55770</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3971</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-59741</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>44638</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108708</v>
+      </c>
+      <c r="C5" t="n">
+        <v>58677</v>
+      </c>
+      <c r="D5" t="n">
+        <v>42208</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-58845</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3659</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-62504</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>44680</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106858</v>
+      </c>
+      <c r="C6" t="n">
+        <v>57850</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41467</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61109</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3502</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-64611</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>44687</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107660</v>
+      </c>
+      <c r="C7" t="n">
+        <v>58413</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41641</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-59806</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-3528</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-63334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>44694</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101941</v>
+      </c>
+      <c r="C8" t="n">
+        <v>53657</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40743</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-60032</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3696</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-63728</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>44701</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100261</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52442</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40250</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-60861</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3829</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-64690</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>44708</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102896</v>
+      </c>
+      <c r="C10" t="n">
+        <v>53656</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41611</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-60788</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3815</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-64603</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>117406</v>
+      </c>
+      <c r="C11" t="n">
+        <v>61290</v>
+      </c>
+      <c r="D11" t="n">
+        <v>48661</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-59164</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-3160</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-62324</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>44988</v>
+      </c>
+      <c r="B12" t="n">
+        <v>120359</v>
+      </c>
+      <c r="C12" t="n">
+        <v>62761</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50078</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-61302</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3187</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-64489</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45009</v>
+      </c>
+      <c r="B13" t="n">
+        <v>124694</v>
+      </c>
+      <c r="C13" t="n">
+        <v>63711</v>
+      </c>
+      <c r="D13" t="n">
+        <v>53358</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-57225</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-3364</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-60589</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B14" t="n">
+        <v>149897</v>
+      </c>
+      <c r="C14" t="n">
+        <v>59070</v>
+      </c>
+      <c r="D14" t="n">
+        <v>83093</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-19499</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1663</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-17836</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45842</v>
+      </c>
+      <c r="B15" t="n">
+        <v>164397</v>
+      </c>
+      <c r="C15" t="n">
+        <v>72002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>84611</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-19645</v>
+      </c>
+      <c r="F15" t="n">
+        <v>319</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-19326</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B16" t="n">
+        <v>166243</v>
+      </c>
+      <c r="C16" t="n">
+        <v>73795</v>
+      </c>
+      <c r="D16" t="n">
+        <v>84692</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-19592</v>
+      </c>
+      <c r="F16" t="n">
+        <v>837</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-18755</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B17" t="n">
+        <v>168569</v>
+      </c>
+      <c r="C17" t="n">
+        <v>75595</v>
+      </c>
+      <c r="D17" t="n">
+        <v>85266</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-19541</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1053</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-18488</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B18" t="n">
+        <v>171848</v>
+      </c>
+      <c r="C18" t="n">
+        <v>78864</v>
+      </c>
+      <c r="D18" t="n">
+        <v>85223</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-19524</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1731</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-17793</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B19" t="n">
+        <v>183598</v>
+      </c>
+      <c r="C19" t="n">
+        <v>72719</v>
+      </c>
+      <c r="D19" t="n">
+        <v>103215</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-19658</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2988</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-16670</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B20" t="n">
+        <v>185047</v>
+      </c>
+      <c r="C20" t="n">
+        <v>74318</v>
+      </c>
+      <c r="D20" t="n">
+        <v>103061</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-17649</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2699</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-14950</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B21" t="n">
+        <v>187432</v>
+      </c>
+      <c r="C21" t="n">
+        <v>72351</v>
+      </c>
+      <c r="D21" t="n">
+        <v>107389</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-17667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3275</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-14392</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B22" t="n">
+        <v>180631</v>
+      </c>
+      <c r="C22" t="n">
+        <v>68580</v>
+      </c>
+      <c r="D22" t="n">
+        <v>104392</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-17620</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3282</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-14338</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B23" t="n">
+        <v>147426</v>
+      </c>
+      <c r="C23" t="n">
+        <v>45537</v>
+      </c>
+      <c r="D23" t="n">
+        <v>94250</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-17667</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1806</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-15861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B24" t="n">
+        <v>159694</v>
+      </c>
+      <c r="C24" t="n">
+        <v>54276</v>
+      </c>
+      <c r="D24" t="n">
+        <v>97742</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-17580</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-15045</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B25" t="n">
         <v>163302</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C25" t="n">
         <v>59442</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D25" t="n">
         <v>96179</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E25" t="n">
         <v>-16577</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F25" t="n">
         <v>2836</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G25" t="n">
         <v>-13741</v>
       </c>
     </row>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1019,6 +1007,29 @@
       </c>
       <c r="G25" t="n">
         <v>-13741</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B26" t="n">
+        <v>160490</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57729</v>
+      </c>
+      <c r="D26" t="n">
+        <v>95063</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-16601</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3123</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-13478</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,29 @@
         <v>-13478</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B27" t="n">
+        <v>162606</v>
+      </c>
+      <c r="C27" t="n">
+        <v>54720</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100210</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-16555</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3736</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-12819</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,29 @@
         <v>-12819</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B28" t="n">
+        <v>164448</v>
+      </c>
+      <c r="C28" t="n">
+        <v>56123</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100637</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-16704</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3355</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-13349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,7 +1063,7 @@
         <v>164448</v>
       </c>
       <c r="C28" t="n">
-        <v>56123</v>
+        <v>56154</v>
       </c>
       <c r="D28" t="n">
         <v>100637</v>
@@ -1076,6 +1076,29 @@
       </c>
       <c r="G28" t="n">
         <v>-13349</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B29" t="n">
+        <v>178366</v>
+      </c>
+      <c r="C29" t="n">
+        <v>63294</v>
+      </c>
+      <c r="D29" t="n">
+        <v>107345</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-16479</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4058</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-12421</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,29 @@
         <v>-12421</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B30" t="n">
+        <v>183501</v>
+      </c>
+      <c r="C30" t="n">
+        <v>67445</v>
+      </c>
+      <c r="D30" t="n">
+        <v>108335</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-16454</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3595</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-12859</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,48 +417,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1134,6 +1122,29 @@
       </c>
       <c r="G30" t="n">
         <v>-12859</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B31" t="n">
+        <v>188450</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66461</v>
+      </c>
+      <c r="D31" t="n">
+        <v>114221</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-16449</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5462</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-10987</v>
       </c>
     </row>
   </sheetData>

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,44 +433,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -481,7 +493,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -527,7 +539,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -550,7 +562,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -573,7 +585,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -688,7 +700,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -803,7 +815,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -826,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -895,7 +907,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -918,7 +930,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -941,7 +953,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -964,7 +976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -987,7 +999,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1056,7 +1068,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1079,7 +1091,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1102,7 +1114,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1125,7 +1137,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,44 +421,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>resmi_rezerv</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>doviz</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>altin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>swap_forward</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>diger</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>swap_toplam</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B2" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B3" t="n">
@@ -516,7 +504,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B5" t="n">
@@ -562,7 +550,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B6" t="n">
@@ -585,7 +573,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +596,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B8" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B9" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B10" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B11" t="n">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B12" t="n">
@@ -723,7 +711,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B13" t="n">
@@ -746,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B14" t="n">
@@ -769,7 +757,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B15" t="n">
@@ -792,7 +780,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B16" t="n">
@@ -815,7 +803,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +826,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B18" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B19" t="n">
@@ -884,7 +872,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B20" t="n">
@@ -907,7 +895,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B21" t="n">
@@ -930,7 +918,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="n">
@@ -953,7 +941,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -976,7 +964,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B24" t="n">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B25" t="n">
@@ -1022,7 +1010,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B26" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B27" t="n">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B28" t="n">
@@ -1091,7 +1079,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B29" t="n">
@@ -1114,7 +1102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B30" t="n">
@@ -1137,7 +1125,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B31" t="n">

--- a/net rezerv/likidite.xlsx
+++ b/net rezerv/likidite.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,29 @@
         <v>-10987</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B32" t="n">
+        <v>188198</v>
+      </c>
+      <c r="C32" t="n">
+        <v>63355</v>
+      </c>
+      <c r="D32" t="n">
+        <v>117089</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-16516</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5793</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-10723</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
